--- a/registration_forms/043_corporate_luncheon_guest_registration_form--registration_forms.xlsx
+++ b/registration_forms/043_corporate_luncheon_guest_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>company_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>company_info</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Contact Email</t>
+          <t>Company Information</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,40 +653,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>guest_type</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Guest Type</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>guest_type</t>
+          <t>job_title_details</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Guest Type</t>
+          <t>Job Title Details</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>guest_type</t>
+          <t>contact_email_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Guest Type</t>
+          <t>Contact Email (Alternative)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Organization</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Contact Email</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,23 +791,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>guest_type_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Guest Category</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -822,10 +822,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -850,7 +850,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>guest_type_choices</t>
+          <t>company_info_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>guest_type_choices</t>
+          <t>company_info_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>guest_type_choices</t>
+          <t>company_info_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>guest_type_choices</t>
+          <t>company_info_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -978,6 +978,74 @@
         </is>
       </c>
       <c r="C9" t="inlineStr">
+        <is>
+          <t>Employee</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>guest_type_2_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>guest_type_2_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Visitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>guest_type_2_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>attendee</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>guest_type_2_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Employee</t>
         </is>
